--- a/test-data/template-bom.xlsx
+++ b/test-data/template-bom.xlsx
@@ -98,7 +98,7 @@
     <t>P</t>
   </si>
   <si>
-    <t>20260531-1</t>
+    <t>20260531-2</t>
   </si>
   <si>
     <t>100400054D@4</t>
